--- a/Demo/LF/lf-integrated-oncho/demo_lf_itas_9999_2_part.xlsx
+++ b/Demo/LF/lf-integrated-oncho/demo_lf_itas_9999_2_part.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12300" tabRatio="500" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
@@ -209,7 +209,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -268,9 +268,6 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -305,15 +302,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -656,450 +644,450 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:U60"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.5"/>
   <cols>
     <col width="24.25" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
     <col width="16.25" customWidth="1" style="8" min="2" max="2"/>
-    <col width="42.625" customWidth="1" style="8" min="3" max="3"/>
+    <col width="42.58203125" customWidth="1" style="8" min="3" max="3"/>
     <col width="41.25" customWidth="1" style="8" min="4" max="4"/>
-    <col width="12.625" customWidth="1" style="8" min="5" max="5"/>
-    <col width="16.875" customWidth="1" style="8" min="6" max="6"/>
+    <col width="12.58203125" customWidth="1" style="8" min="5" max="5"/>
+    <col width="16.83203125" customWidth="1" style="8" min="6" max="6"/>
     <col width="29.5" customWidth="1" style="8" min="7" max="7"/>
-    <col width="17.875" customWidth="1" style="8" min="8" max="8"/>
-    <col width="19.625" customWidth="1" style="8" min="9" max="9"/>
+    <col width="17.83203125" customWidth="1" style="8" min="8" max="8"/>
+    <col width="32.1640625" customWidth="1" style="8" min="9" max="9"/>
     <col width="9.75" customWidth="1" style="8" min="10" max="10"/>
-    <col width="20.625" customWidth="1" style="8" min="11" max="11"/>
-    <col width="9.125" customWidth="1" style="8" min="12" max="12"/>
+    <col width="20.58203125" customWidth="1" style="8" min="11" max="11"/>
+    <col width="9.08203125" customWidth="1" style="8" min="12" max="12"/>
     <col width="20.5" customWidth="1" style="8" min="13" max="13"/>
     <col width="11" customWidth="1" style="8" min="14" max="15"/>
     <col width="11.75" bestFit="1" customWidth="1" style="8" min="16" max="16"/>
-    <col width="22.125" bestFit="1" customWidth="1" style="8" min="17" max="19"/>
+    <col width="22.08203125" bestFit="1" customWidth="1" style="8" min="17" max="19"/>
     <col width="18" bestFit="1" customWidth="1" style="8" min="20" max="21"/>
     <col width="11" customWidth="1" style="8" min="22" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customFormat="1" customHeight="1" s="37">
-      <c r="A1" s="23" t="inlineStr">
+    <row r="1" ht="31" customFormat="1" customHeight="1" s="7">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="B1" s="23" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="23" t="inlineStr">
+      <c r="C1" s="22" t="inlineStr">
         <is>
           <t>label::English (en)</t>
         </is>
       </c>
-      <c r="D1" s="23" t="inlineStr">
+      <c r="D1" s="22" t="inlineStr">
         <is>
           <t>hint::English (en)</t>
         </is>
       </c>
-      <c r="E1" s="23" t="inlineStr">
+      <c r="E1" s="22" t="inlineStr">
         <is>
           <t>appearance</t>
         </is>
       </c>
-      <c r="F1" s="23" t="inlineStr">
+      <c r="F1" s="22" t="inlineStr">
         <is>
           <t>constraint</t>
         </is>
       </c>
-      <c r="G1" s="23" t="inlineStr">
+      <c r="G1" s="22" t="inlineStr">
         <is>
           <t>constraint_message::English (en)</t>
         </is>
       </c>
-      <c r="H1" s="23" t="inlineStr">
+      <c r="H1" s="22" t="inlineStr">
         <is>
           <t>relevant</t>
         </is>
       </c>
-      <c r="I1" s="23" t="inlineStr">
+      <c r="I1" s="22" t="inlineStr">
         <is>
           <t>calculation</t>
         </is>
       </c>
-      <c r="J1" s="23" t="inlineStr">
+      <c r="J1" s="22" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="K1" s="23" t="inlineStr">
+      <c r="K1" s="22" t="inlineStr">
         <is>
           <t>required_message::English (en)</t>
         </is>
       </c>
-      <c r="L1" s="23" t="inlineStr">
+      <c r="L1" s="22" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="M1" s="24" t="inlineStr">
+      <c r="M1" s="23" t="inlineStr">
         <is>
           <t>choice_filter</t>
         </is>
       </c>
-      <c r="N1" s="25" t="inlineStr">
+      <c r="N1" s="24" t="inlineStr">
         <is>
           <t>readonly</t>
         </is>
       </c>
-      <c r="O1" s="26" t="inlineStr">
+      <c r="O1" s="25" t="inlineStr">
         <is>
           <t>bind::type</t>
         </is>
       </c>
-      <c r="P1" s="26" t="inlineStr">
+      <c r="P1" s="25" t="inlineStr">
         <is>
           <t>bind::db_get</t>
         </is>
       </c>
-      <c r="Q1" s="26" t="inlineStr">
+      <c r="Q1" s="25" t="inlineStr">
         <is>
           <t>bind::db_filter_by_col_1</t>
         </is>
       </c>
-      <c r="R1" s="26" t="inlineStr">
+      <c r="R1" s="25" t="inlineStr">
         <is>
           <t>bind::db_filter_by_col_2</t>
         </is>
       </c>
-      <c r="S1" s="26" t="inlineStr">
+      <c r="S1" s="25" t="inlineStr">
         <is>
           <t>bind::db_filter_by_col_3</t>
         </is>
       </c>
-      <c r="T1" s="26" t="inlineStr">
+      <c r="T1" s="25" t="inlineStr">
         <is>
           <t>bind::db_add_col_4</t>
         </is>
       </c>
-      <c r="U1" s="26" t="inlineStr">
+      <c r="U1" s="25" t="inlineStr">
         <is>
           <t>bind::db_add_col_5</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="47.25" customFormat="1" customHeight="1" s="37">
+    <row r="2" ht="46.5" customFormat="1" customHeight="1" s="7">
       <c r="A2" s="17" t="inlineStr">
         <is>
           <t>select_one recorder_list</t>
         </is>
       </c>
-      <c r="B2" s="36" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>recorder</t>
         </is>
       </c>
-      <c r="C2" s="36" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Enter Recorder ID</t>
         </is>
       </c>
-      <c r="D2" s="36" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>If you are the only recorder on your team, this may be called a "team ID". Recorder ID is the 2-digit code assigned to you or your team.</t>
         </is>
       </c>
-      <c r="F2" s="27" t="n"/>
+      <c r="F2" s="26" t="n"/>
       <c r="G2" s="5" t="n"/>
-      <c r="J2" s="36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="N2" s="36" t="n"/>
-      <c r="O2" s="36" t="n"/>
-      <c r="P2" s="36" t="n"/>
-      <c r="Q2" s="36" t="n"/>
-      <c r="R2" s="36" t="n"/>
-      <c r="S2" s="36" t="n"/>
-      <c r="T2" s="36" t="n"/>
-      <c r="U2" s="36" t="n"/>
-    </row>
-    <row r="3" customFormat="1" s="37">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="n"/>
+      <c r="O2" s="6" t="n"/>
+      <c r="P2" s="6" t="n"/>
+      <c r="Q2" s="6" t="n"/>
+      <c r="R2" s="6" t="n"/>
+      <c r="S2" s="6" t="n"/>
+      <c r="T2" s="6" t="n"/>
+      <c r="U2" s="6" t="n"/>
+    </row>
+    <row r="3" customFormat="1" s="7">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B3" s="36" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>admin1</t>
         </is>
       </c>
-      <c r="C3" s="36" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Select your State/Region/Province</t>
         </is>
       </c>
-      <c r="D3" s="36" t="n"/>
-      <c r="F3" s="27" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="F3" s="26" t="n"/>
       <c r="G3" s="5" t="n"/>
-      <c r="J3" s="36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="N3" s="36" t="n"/>
-      <c r="O3" s="36" t="n"/>
-      <c r="P3" s="28" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="n"/>
+      <c r="O3" s="6" t="n"/>
+      <c r="P3" s="27" t="inlineStr">
         <is>
           <t>col_1</t>
         </is>
       </c>
-      <c r="Q3" s="36" t="n"/>
-      <c r="R3" s="36" t="n"/>
-      <c r="S3" s="36" t="n"/>
-      <c r="T3" s="36" t="n"/>
-      <c r="U3" s="36" t="n"/>
-    </row>
-    <row r="4" customFormat="1" s="37">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="Q3" s="6" t="n"/>
+      <c r="R3" s="6" t="n"/>
+      <c r="S3" s="6" t="n"/>
+      <c r="T3" s="6" t="n"/>
+      <c r="U3" s="6" t="n"/>
+    </row>
+    <row r="4" customFormat="1" s="7">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>iu</t>
         </is>
       </c>
-      <c r="C4" s="36" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Select your Implementation Unit (IU)</t>
         </is>
       </c>
-      <c r="D4" s="36" t="n"/>
-      <c r="F4" s="27" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="F4" s="26" t="n"/>
       <c r="G4" s="5" t="n"/>
-      <c r="J4" s="36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="N4" s="36" t="n"/>
-      <c r="O4" s="36" t="n"/>
-      <c r="P4" s="37" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="n"/>
+      <c r="O4" s="6" t="n"/>
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>col_2</t>
         </is>
       </c>
-      <c r="Q4" s="28" t="inlineStr">
+      <c r="Q4" s="27" t="inlineStr">
         <is>
           <t>${admin1}</t>
         </is>
       </c>
-      <c r="R4" s="36" t="n"/>
-      <c r="S4" s="36" t="n"/>
-      <c r="T4" s="36" t="n"/>
-      <c r="U4" s="36" t="n"/>
-    </row>
-    <row r="5" customFormat="1" s="37">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="R4" s="6" t="n"/>
+      <c r="S4" s="6" t="n"/>
+      <c r="T4" s="6" t="n"/>
+      <c r="U4" s="6" t="n"/>
+    </row>
+    <row r="5" customFormat="1" s="7">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Select your site</t>
         </is>
       </c>
-      <c r="D5" s="36" t="n"/>
-      <c r="F5" s="27" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="F5" s="26" t="n"/>
       <c r="G5" s="5" t="n"/>
-      <c r="J5" s="36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="N5" s="36" t="n"/>
-      <c r="O5" s="36" t="n"/>
-      <c r="P5" s="37" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="n"/>
+      <c r="O5" s="6" t="n"/>
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>col_3</t>
         </is>
       </c>
-      <c r="R5" s="28" t="inlineStr">
+      <c r="R5" s="27" t="inlineStr">
         <is>
           <t>${iu}</t>
         </is>
       </c>
-      <c r="S5" s="36" t="n"/>
-      <c r="T5" s="36" t="n"/>
-      <c r="U5" s="36" t="n"/>
-    </row>
-    <row r="6" customFormat="1" s="37">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="S5" s="6" t="n"/>
+      <c r="T5" s="6" t="n"/>
+      <c r="U5" s="6" t="n"/>
+    </row>
+    <row r="6" customFormat="1" s="7">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>site_id</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Select your site code</t>
         </is>
       </c>
-      <c r="D6" s="36" t="n"/>
-      <c r="F6" s="27" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="F6" s="26" t="n"/>
       <c r="G6" s="5" t="n"/>
-      <c r="J6" s="36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="N6" s="36" t="n"/>
-      <c r="O6" s="36" t="n"/>
-      <c r="P6" s="37" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="6" t="n"/>
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>col_4</t>
         </is>
       </c>
-      <c r="Q6" s="36" t="n"/>
-      <c r="R6" s="36" t="n"/>
-      <c r="S6" s="37" t="inlineStr">
+      <c r="Q6" s="6" t="n"/>
+      <c r="R6" s="6" t="n"/>
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>${site}</t>
         </is>
       </c>
-      <c r="T6" s="36" t="n"/>
-      <c r="U6" s="36" t="n"/>
-    </row>
-    <row r="7" ht="47.25" customFormat="1" customHeight="1" s="37">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="T6" s="6" t="n"/>
+      <c r="U6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="46.5" customFormat="1" customHeight="1" s="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>select_one id_type</t>
         </is>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>id_type</t>
         </is>
       </c>
-      <c r="C7" s="36" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Participant ID Code method :</t>
         </is>
       </c>
-      <c r="D7" s="36" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Will you scann the barcode/Qrcode, use the auto-generated code by the form or enter the code manualy ?</t>
         </is>
       </c>
-      <c r="E7" s="36" t="n"/>
-      <c r="G7" s="36" t="n"/>
-      <c r="H7" s="36" t="n"/>
-      <c r="I7" s="36" t="n"/>
-      <c r="J7" s="36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K7" s="36" t="n"/>
-      <c r="L7" s="36" t="n"/>
-      <c r="M7" s="36" t="n"/>
-      <c r="O7" s="28" t="n"/>
-    </row>
-    <row r="8" ht="94.5" customFormat="1" customHeight="1" s="37">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="E7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="O7" s="27" t="n"/>
+    </row>
+    <row r="8" ht="93" customFormat="1" customHeight="1" s="7">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>select_one warning_note</t>
         </is>
       </c>
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>warning_note1</t>
         </is>
       </c>
-      <c r="C8" s="36" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Important Note for Recorders: With Auto-Generated ID code option, only one phone/tablet must be used to record all participants at this Community/Village (survey site). Using multiple devices may cause duplicate ID codes, compromising data integrity.</t>
         </is>
       </c>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
-      <c r="G8" s="36" t="n"/>
-      <c r="H8" s="36" t="inlineStr">
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>${id_type} = 'Auto-generated codes'</t>
         </is>
       </c>
-      <c r="I8" s="36" t="n"/>
-      <c r="J8" s="36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K8" s="36" t="n"/>
-      <c r="L8" s="36" t="n"/>
-      <c r="M8" s="36" t="n"/>
-      <c r="O8" s="28" t="n"/>
-    </row>
-    <row r="9" ht="94.5" customFormat="1" customHeight="1" s="37">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
+      <c r="O8" s="27" t="n"/>
+    </row>
+    <row r="9" ht="93" customFormat="1" customHeight="1" s="7">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>select_one warning_note</t>
         </is>
       </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>warning_note2</t>
         </is>
       </c>
-      <c r="C9" s="36" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Important Note for Recorders: To avoid duplicate codes, Use the "Save as draft" option if you haven’t finished registering all participants of this Community/Village (survey site). If you need to resume, reopen your draft from the "Saved Forms" list to continue.</t>
         </is>
       </c>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="36" t="n"/>
-      <c r="G9" s="36" t="n"/>
-      <c r="H9" s="36" t="inlineStr">
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>${id_type} = 'Scanner' or ${id_type} = 'Manual numbering'</t>
         </is>
       </c>
-      <c r="I9" s="36" t="n"/>
-      <c r="J9" s="36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K9" s="36" t="n"/>
-      <c r="L9" s="36" t="n"/>
-      <c r="M9" s="36" t="n"/>
-      <c r="O9" s="28" t="n"/>
-    </row>
-    <row r="10" customFormat="1" s="37">
-      <c r="C10" s="36" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="36" t="n"/>
-      <c r="G10" s="36" t="n"/>
-      <c r="H10" s="36" t="n"/>
-      <c r="I10" s="36" t="n"/>
-      <c r="J10" s="36" t="n"/>
-      <c r="K10" s="36" t="n"/>
-      <c r="L10" s="36" t="n"/>
-      <c r="M10" s="36" t="n"/>
-      <c r="O10" s="28" t="n"/>
-    </row>
-    <row r="11" customFormat="1" s="37">
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n"/>
+      <c r="O9" s="27" t="n"/>
+    </row>
+    <row r="10" customFormat="1" s="7">
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="n"/>
+      <c r="O10" s="27" t="n"/>
+    </row>
+    <row r="11" customFormat="1" s="7">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>calculate</t>
@@ -1132,18 +1120,18 @@
         </is>
       </c>
     </row>
-    <row r="12" customFormat="1" s="37">
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="G12" s="36" t="n"/>
-      <c r="H12" s="36" t="n"/>
-      <c r="I12" s="36" t="n"/>
-      <c r="J12" s="36" t="n"/>
-      <c r="K12" s="36" t="n"/>
-      <c r="L12" s="36" t="n"/>
-    </row>
-    <row r="13" customFormat="1" s="37">
+    <row r="12" customFormat="1" s="7">
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
+    </row>
+    <row r="13" customFormat="1" s="7">
       <c r="A13" s="15" t="inlineStr">
         <is>
           <t>calculate</t>
@@ -1170,37 +1158,37 @@
       <c r="L13" s="16" t="n"/>
       <c r="M13" s="15" t="n"/>
       <c r="N13" s="15" t="n"/>
-      <c r="O13" s="29" t="inlineStr">
+      <c r="O13" s="28" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
     </row>
-    <row r="14" customFormat="1" s="37">
-      <c r="A14" s="37" t="inlineStr">
+    <row r="14" customFormat="1" s="7">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>begin repeat</t>
         </is>
       </c>
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>pi999</t>
         </is>
       </c>
-      <c r="C14" s="36" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Participant</t>
         </is>
       </c>
-      <c r="D14" s="36" t="n"/>
-      <c r="G14" s="36" t="n"/>
-      <c r="H14" s="36" t="n"/>
-      <c r="I14" s="36" t="n"/>
-      <c r="J14" s="36" t="n"/>
-      <c r="K14" s="36" t="n"/>
-      <c r="L14" s="36" t="n"/>
-    </row>
-    <row r="15" customFormat="1" s="37">
+      <c r="D14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
+    </row>
+    <row r="15" customFormat="1" s="7">
       <c r="A15" s="15" t="inlineStr">
         <is>
           <t>calculate</t>
@@ -1233,7 +1221,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="63" customFormat="1" customHeight="1" s="37">
+    <row r="16" ht="31" customFormat="1" customHeight="1" s="7">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>calculate</t>
@@ -1266,60 +1254,60 @@
         </is>
       </c>
     </row>
-    <row r="17" customFormat="1" s="37">
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="G17" s="36" t="n"/>
-      <c r="H17" s="36" t="n"/>
-      <c r="I17" s="36" t="n"/>
-      <c r="J17" s="36" t="n"/>
-      <c r="K17" s="36" t="n"/>
-      <c r="L17" s="36" t="n"/>
-    </row>
-    <row r="18" customFormat="1" s="37">
-      <c r="A18" s="37" t="inlineStr">
+    <row r="17" customFormat="1" s="7">
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n"/>
+    </row>
+    <row r="18" customFormat="1" s="7">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>select_one yes_no</t>
         </is>
       </c>
-      <c r="B18" s="36" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>consent</t>
         </is>
       </c>
-      <c r="C18" s="36" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>Did the participant give consent to blood tests?</t>
         </is>
       </c>
-      <c r="D18" s="36" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>"No" answer response will end survey</t>
         </is>
       </c>
-      <c r="G18" s="36" t="n"/>
-      <c r="H18" s="36" t="n"/>
-      <c r="I18" s="36" t="n"/>
-      <c r="J18" s="36" t="n"/>
-      <c r="K18" s="36" t="n"/>
-      <c r="L18" s="36" t="n"/>
-      <c r="O18" s="28" t="n"/>
-    </row>
-    <row r="19" customFormat="1" s="37">
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
-      <c r="G19" s="36" t="n"/>
-      <c r="I19" s="36" t="n"/>
-      <c r="J19" s="36" t="n"/>
-      <c r="K19" s="36" t="n"/>
-      <c r="L19" s="36" t="n"/>
-      <c r="M19" s="36" t="n"/>
-      <c r="O19" s="28" t="n"/>
-    </row>
-    <row r="20" ht="31.5" customFormat="1" customHeight="1" s="37">
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
+      <c r="O18" s="27" t="n"/>
+    </row>
+    <row r="19" customFormat="1" s="7">
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
+      <c r="M19" s="6" t="n"/>
+      <c r="O19" s="27" t="n"/>
+    </row>
+    <row r="20" customFormat="1" s="7">
       <c r="A20" s="10" t="inlineStr">
         <is>
           <t>integer</t>
@@ -1362,9 +1350,9 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="O20" s="30" t="n"/>
-    </row>
-    <row r="21" ht="47.25" customFormat="1" customHeight="1" s="37">
+      <c r="O20" s="29" t="n"/>
+    </row>
+    <row r="21" ht="31" customFormat="1" customHeight="1" s="7">
       <c r="A21" s="10" t="inlineStr">
         <is>
           <t>calculate</t>
@@ -1395,9 +1383,9 @@
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="9" t="n"/>
       <c r="N21" s="10" t="n"/>
-      <c r="O21" s="30" t="n"/>
-    </row>
-    <row r="22" customFormat="1" s="37">
+      <c r="O21" s="29" t="n"/>
+    </row>
+    <row r="22" customFormat="1" s="7">
       <c r="A22" s="10" t="inlineStr">
         <is>
           <t>calculate</t>
@@ -1430,20 +1418,20 @@
       <c r="N22" s="10" t="n"/>
       <c r="O22" s="10" t="n"/>
     </row>
-    <row r="23" customFormat="1" s="37">
-      <c r="C23" s="36" t="n"/>
-      <c r="D23" s="36" t="n"/>
-      <c r="E23" s="36" t="n"/>
-      <c r="F23" s="36" t="n"/>
-      <c r="G23" s="36" t="n"/>
-      <c r="I23" s="36" t="n"/>
-      <c r="J23" s="36" t="n"/>
-      <c r="K23" s="36" t="n"/>
-      <c r="L23" s="36" t="n"/>
-      <c r="M23" s="36" t="n"/>
-      <c r="O23" s="28" t="n"/>
-    </row>
-    <row r="24" customFormat="1" s="37">
+    <row r="23" customFormat="1" s="7">
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6" t="n"/>
+      <c r="O23" s="27" t="n"/>
+    </row>
+    <row r="24" customFormat="1" s="7">
       <c r="A24" s="11" t="inlineStr">
         <is>
           <t>integer</t>
@@ -1478,9 +1466,9 @@
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="12" t="n"/>
       <c r="N24" s="11" t="n"/>
-      <c r="O24" s="31" t="n"/>
-    </row>
-    <row r="25" ht="31.5" customFormat="1" customHeight="1" s="37">
+      <c r="O24" s="30" t="n"/>
+    </row>
+    <row r="25" ht="31" customFormat="1" customHeight="1" s="7">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>calculate</t>
@@ -1511,22 +1499,22 @@
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="12" t="n"/>
       <c r="N25" s="11" t="n"/>
-      <c r="O25" s="31" t="n"/>
-    </row>
-    <row r="26" customFormat="1" s="37">
-      <c r="C26" s="36" t="n"/>
-      <c r="D26" s="36" t="n"/>
-      <c r="E26" s="36" t="n"/>
-      <c r="F26" s="36" t="n"/>
-      <c r="G26" s="36" t="n"/>
-      <c r="I26" s="36" t="n"/>
-      <c r="J26" s="36" t="n"/>
-      <c r="K26" s="36" t="n"/>
-      <c r="L26" s="36" t="n"/>
-      <c r="M26" s="36" t="n"/>
-      <c r="O26" s="28" t="n"/>
-    </row>
-    <row r="27" customFormat="1" s="37">
+      <c r="O25" s="30" t="n"/>
+    </row>
+    <row r="26" customFormat="1" s="7">
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="6" t="n"/>
+      <c r="L26" s="6" t="n"/>
+      <c r="M26" s="6" t="n"/>
+      <c r="O26" s="27" t="n"/>
+    </row>
+    <row r="27" customFormat="1" s="7">
       <c r="A27" s="13" t="inlineStr">
         <is>
           <t>select_one barcode_method</t>
@@ -1561,9 +1549,9 @@
       <c r="L27" s="14" t="n"/>
       <c r="M27" s="14" t="n"/>
       <c r="N27" s="13" t="n"/>
-      <c r="O27" s="32" t="n"/>
-    </row>
-    <row r="28" ht="31.5" customFormat="1" customHeight="1" s="37">
+      <c r="O27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="31" customFormat="1" customHeight="1" s="7">
       <c r="A28" s="13" t="inlineStr">
         <is>
           <t>barcode</t>
@@ -1598,9 +1586,9 @@
       <c r="L28" s="14" t="n"/>
       <c r="M28" s="14" t="n"/>
       <c r="N28" s="13" t="n"/>
-      <c r="O28" s="32" t="n"/>
-    </row>
-    <row r="29" ht="31.5" customFormat="1" customHeight="1" s="37">
+      <c r="O28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="31" customFormat="1" customHeight="1" s="7">
       <c r="A29" s="13" t="inlineStr">
         <is>
           <t>text</t>
@@ -1635,32 +1623,32 @@
       <c r="L29" s="14" t="n"/>
       <c r="M29" s="14" t="n"/>
       <c r="N29" s="13" t="n"/>
-      <c r="O29" s="32" t="n"/>
-    </row>
-    <row r="30" customFormat="1" s="37">
-      <c r="A30" s="32" t="inlineStr">
+      <c r="O29" s="31" t="n"/>
+    </row>
+    <row r="30" customFormat="1" s="7">
+      <c r="A30" s="31" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B30" s="32" t="inlineStr">
+      <c r="B30" s="31" t="inlineStr">
         <is>
           <t>code_id5</t>
         </is>
       </c>
-      <c r="C30" s="32" t="inlineStr">
+      <c r="C30" s="31" t="inlineStr">
         <is>
           <t>Please re-enter the QR code / Barcode</t>
         </is>
       </c>
-      <c r="D30" s="32" t="n"/>
-      <c r="E30" s="32" t="n"/>
-      <c r="F30" s="32" t="inlineStr">
+      <c r="D30" s="31" t="n"/>
+      <c r="E30" s="31" t="n"/>
+      <c r="F30" s="31" t="inlineStr">
         <is>
           <t>. = ${code_id4}</t>
         </is>
       </c>
-      <c r="G30" s="32" t="inlineStr">
+      <c r="G30" s="31" t="inlineStr">
         <is>
           <t>The repeated code must be the same as previouly entered</t>
         </is>
@@ -1671,31 +1659,31 @@
         </is>
       </c>
       <c r="I30" s="14" t="n"/>
-      <c r="J30" s="32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K30" s="32" t="n"/>
-      <c r="L30" s="32" t="n"/>
-      <c r="M30" s="32" t="n"/>
-      <c r="N30" s="32" t="n"/>
-      <c r="O30" s="32" t="n"/>
-    </row>
-    <row r="31" customFormat="1" s="37">
-      <c r="C31" s="36" t="n"/>
-      <c r="D31" s="36" t="n"/>
-      <c r="E31" s="36" t="n"/>
-      <c r="F31" s="36" t="n"/>
-      <c r="G31" s="36" t="n"/>
-      <c r="I31" s="36" t="n"/>
-      <c r="J31" s="36" t="n"/>
-      <c r="K31" s="36" t="n"/>
-      <c r="L31" s="36" t="n"/>
-      <c r="M31" s="36" t="n"/>
-      <c r="O31" s="28" t="n"/>
-    </row>
-    <row r="32" ht="36" customFormat="1" customHeight="1" s="37">
+      <c r="J30" s="31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K30" s="31" t="n"/>
+      <c r="L30" s="31" t="n"/>
+      <c r="M30" s="31" t="n"/>
+      <c r="N30" s="31" t="n"/>
+      <c r="O30" s="31" t="n"/>
+    </row>
+    <row r="31" customFormat="1" s="7">
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="I31" s="6" t="n"/>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="6" t="n"/>
+      <c r="L31" s="6" t="n"/>
+      <c r="M31" s="6" t="n"/>
+      <c r="O31" s="27" t="n"/>
+    </row>
+    <row r="32" ht="36" customFormat="1" customHeight="1" s="7">
       <c r="A32" s="15" t="inlineStr">
         <is>
           <t>text</t>
@@ -1741,180 +1729,180 @@
       <c r="K32" s="15" t="n"/>
       <c r="L32" s="15" t="n"/>
       <c r="M32" s="15" t="n"/>
-      <c r="N32" s="29" t="inlineStr">
+      <c r="N32" s="28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
-      <c r="T32" s="28" t="inlineStr">
+      <c r="T32" s="27" t="inlineStr">
         <is>
           <t>${site_id}</t>
         </is>
       </c>
-      <c r="U32" s="33" t="inlineStr">
+      <c r="U32" s="32" t="inlineStr">
         <is>
           <t>.</t>
         </is>
       </c>
     </row>
-    <row r="33" customFormat="1" s="37">
-      <c r="B33" s="36" t="n"/>
-      <c r="C33" s="36" t="n"/>
-      <c r="D33" s="36" t="n"/>
-      <c r="J33" s="36" t="n"/>
-    </row>
-    <row r="34" customFormat="1" s="37">
-      <c r="A34" s="37" t="inlineStr">
+    <row r="33" customFormat="1" s="7">
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="J33" s="6" t="n"/>
+    </row>
+    <row r="34" customFormat="1" s="7">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>select_one sex_list</t>
         </is>
       </c>
-      <c r="B34" s="36" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>sex</t>
         </is>
       </c>
-      <c r="C34" s="36" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>Sex of respondent</t>
         </is>
       </c>
-      <c r="D34" s="36" t="n"/>
-      <c r="E34" s="36" t="n"/>
-      <c r="F34" s="36" t="n"/>
-      <c r="G34" s="36" t="n"/>
-      <c r="H34" s="37" t="inlineStr">
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">${consent} = 'Yes' </t>
         </is>
       </c>
-      <c r="I34" s="36" t="n"/>
-      <c r="J34" s="36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K34" s="36" t="n"/>
-      <c r="L34" s="36" t="n"/>
-      <c r="M34" s="36" t="n"/>
-    </row>
-    <row r="35" customFormat="1" s="37">
-      <c r="A35" s="37" t="inlineStr">
+      <c r="I34" s="6" t="n"/>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="n"/>
+      <c r="L34" s="6" t="n"/>
+      <c r="M34" s="6" t="n"/>
+    </row>
+    <row r="35" customFormat="1" s="7">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B35" s="36" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>id_household</t>
         </is>
       </c>
-      <c r="C35" s="36" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>Household ID</t>
         </is>
       </c>
-      <c r="D35" s="36" t="n"/>
-      <c r="E35" s="36" t="n"/>
-      <c r="F35" s="36" t="n"/>
-      <c r="G35" s="36" t="n"/>
-      <c r="H35" s="37" t="inlineStr">
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">${consent} = 'Yes' </t>
         </is>
       </c>
-      <c r="I35" s="36" t="n"/>
-      <c r="J35" s="36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K35" s="36" t="n"/>
-      <c r="L35" s="36" t="n"/>
-      <c r="M35" s="36" t="n"/>
-    </row>
-    <row r="36" ht="31.5" customFormat="1" customHeight="1" s="37">
-      <c r="A36" s="37" t="inlineStr">
+      <c r="I35" s="6" t="n"/>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="n"/>
+      <c r="L35" s="6" t="n"/>
+      <c r="M35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="31" customFormat="1" customHeight="1" s="7">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B36" s="36" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>id_surveyed</t>
         </is>
       </c>
-      <c r="C36" s="36" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>Surveyed Number  (${recorder}${id_household}...)</t>
         </is>
       </c>
-      <c r="D36" s="36" t="n"/>
-      <c r="E36" s="36" t="n"/>
-      <c r="F36" s="36" t="n"/>
-      <c r="G36" s="36" t="n"/>
-      <c r="H36" s="37" t="inlineStr">
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">${consent} = 'Yes' </t>
         </is>
       </c>
-      <c r="I36" s="36" t="n"/>
-      <c r="J36" s="36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K36" s="36" t="n"/>
-      <c r="L36" s="36" t="n"/>
-      <c r="M36" s="36" t="n"/>
-    </row>
-    <row r="37" ht="63" customFormat="1" customHeight="1" s="37">
-      <c r="A37" s="37" t="inlineStr">
+      <c r="I36" s="6" t="n"/>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="n"/>
+      <c r="L36" s="6" t="n"/>
+      <c r="M36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="46.5" customFormat="1" customHeight="1" s="7">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B37" s="36" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>id_surveyed_full</t>
         </is>
       </c>
-      <c r="C37" s="36" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>Full Surveyed Number</t>
         </is>
       </c>
-      <c r="D37" s="36" t="n"/>
-      <c r="E37" s="36" t="n"/>
-      <c r="F37" s="36" t="n"/>
-      <c r="G37" s="36" t="n"/>
-      <c r="H37" s="37" t="inlineStr">
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">${consent} = 'Yes' </t>
         </is>
       </c>
-      <c r="I37" s="36" t="inlineStr">
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>concat(${site_id}, '-',${recorder},'-', ${id_household},'-',${id_surveyed})</t>
         </is>
       </c>
-      <c r="J37" s="36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K37" s="36" t="n"/>
-      <c r="L37" s="36" t="n"/>
-      <c r="M37" s="36" t="n"/>
-      <c r="N37" s="37" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customFormat="1" customHeight="1" s="37">
-      <c r="A38" s="37" t="inlineStr">
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="n"/>
+      <c r="L37" s="6" t="n"/>
+      <c r="M37" s="6" t="n"/>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customFormat="1" customHeight="1" s="7">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
@@ -1924,37 +1912,37 @@
           <t>age_yrs</t>
         </is>
       </c>
-      <c r="C38" s="36" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>Enter age in years</t>
         </is>
       </c>
-      <c r="D38" s="36" t="n"/>
-      <c r="E38" s="36" t="n"/>
-      <c r="F38" s="36" t="inlineStr">
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> . &gt;= 20</t>
         </is>
       </c>
-      <c r="G38" s="36" t="inlineStr">
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>The age must be 20 years or more</t>
         </is>
       </c>
-      <c r="H38" s="37" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">${consent} = 'Yes' </t>
         </is>
       </c>
-      <c r="I38" s="36" t="n"/>
-      <c r="J38" s="36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K38" s="36" t="n"/>
-      <c r="L38" s="36" t="n"/>
-      <c r="M38" s="36" t="n"/>
+      <c r="I38" s="6" t="n"/>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="n"/>
+      <c r="L38" s="6" t="n"/>
+      <c r="M38" s="6" t="n"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
@@ -1982,7 +1970,7 @@
           <t>The value must not be greater than the age</t>
         </is>
       </c>
-      <c r="H39" s="37" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">${consent} = 'Yes' </t>
         </is>
@@ -1994,7 +1982,7 @@
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="37" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>select_one yes_no</t>
         </is>
@@ -2009,7 +1997,7 @@
           <t>Are you from another village/city/location?</t>
         </is>
       </c>
-      <c r="H40" s="37" t="inlineStr">
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">${consent} = 'Yes' </t>
         </is>
@@ -2036,7 +2024,7 @@
           <t>Precedents Village/city/location</t>
         </is>
       </c>
-      <c r="H41" s="37" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>${come_from_another_location} = 'Yes'</t>
         </is>
@@ -2063,7 +2051,7 @@
           <t>Profession</t>
         </is>
       </c>
-      <c r="H42" s="37" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">${consent} = 'Yes' </t>
         </is>
@@ -2090,7 +2078,7 @@
           <t>Education Level</t>
         </is>
       </c>
-      <c r="H43" s="37" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>${consent} = 'Yes'</t>
         </is>
@@ -2102,7 +2090,7 @@
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="37" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>select_one yes_no</t>
         </is>
@@ -2117,7 +2105,7 @@
           <t>Have you ever swallowed LF medicines (Y/N)?</t>
         </is>
       </c>
-      <c r="H44" s="37" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">${consent} = 'Yes' </t>
         </is>
@@ -2139,12 +2127,12 @@
           <t>time_taken_med</t>
         </is>
       </c>
-      <c r="C45" s="34" t="inlineStr">
+      <c r="C45" s="33" t="inlineStr">
         <is>
           <t>How many times taken?</t>
         </is>
       </c>
-      <c r="H45" s="37" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> ${swallow_med} = 'Yes' </t>
         </is>
@@ -2156,7 +2144,7 @@
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="37" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>select_one yes_no</t>
         </is>
@@ -2166,12 +2154,12 @@
           <t>why_never_treated</t>
         </is>
       </c>
-      <c r="C46" s="34" t="inlineStr">
+      <c r="C46" s="33" t="inlineStr">
         <is>
           <t>Why were you never treated?</t>
         </is>
       </c>
-      <c r="H46" s="37" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> ${swallow_med} = 'No' </t>
         </is>
@@ -2182,8 +2170,8 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="15.75" customFormat="1" customHeight="1" s="37">
-      <c r="A47" s="37" t="inlineStr">
+    <row r="47" ht="15.75" customFormat="1" customHeight="1" s="7">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>select_one yes_no</t>
         </is>
@@ -2193,32 +2181,32 @@
           <t>mosquito_net</t>
         </is>
       </c>
-      <c r="C47" s="36" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>Do you have mosquito net? (Y/N)</t>
         </is>
       </c>
-      <c r="D47" s="36" t="n"/>
-      <c r="E47" s="36" t="n"/>
-      <c r="F47" s="36" t="n"/>
-      <c r="G47" s="36" t="n"/>
-      <c r="H47" s="37" t="inlineStr">
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n"/>
+      <c r="F47" s="6" t="n"/>
+      <c r="G47" s="6" t="n"/>
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">${consent} = 'Yes' </t>
         </is>
       </c>
-      <c r="I47" s="36" t="n"/>
+      <c r="I47" s="6" t="n"/>
       <c r="J47" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K47" s="36" t="n"/>
-      <c r="L47" s="36" t="n"/>
-      <c r="M47" s="36" t="n"/>
-    </row>
-    <row r="48" ht="15.75" customFormat="1" customHeight="1" s="37">
-      <c r="A48" s="37" t="inlineStr">
+      <c r="K47" s="6" t="n"/>
+      <c r="L47" s="6" t="n"/>
+      <c r="M47" s="6" t="n"/>
+    </row>
+    <row r="48" ht="15.75" customFormat="1" customHeight="1" s="7">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>select_one yes_no</t>
         </is>
@@ -2228,32 +2216,32 @@
           <t>sleep_mosq_net</t>
         </is>
       </c>
-      <c r="C48" s="36" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>Do you sleep inside mosquito net? (Y/N)</t>
         </is>
       </c>
-      <c r="D48" s="36" t="n"/>
-      <c r="E48" s="36" t="n"/>
-      <c r="F48" s="36" t="n"/>
-      <c r="G48" s="36" t="n"/>
-      <c r="H48" s="37" t="inlineStr">
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="6" t="n"/>
+      <c r="G48" s="6" t="n"/>
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">${consent} = 'Yes'  and ${mosquito_net} = 'Yes' </t>
         </is>
       </c>
-      <c r="I48" s="36" t="n"/>
+      <c r="I48" s="6" t="n"/>
       <c r="J48" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K48" s="36" t="n"/>
-      <c r="L48" s="36" t="n"/>
-      <c r="M48" s="36" t="n"/>
-    </row>
-    <row r="49" ht="15.75" customFormat="1" customHeight="1" s="37">
-      <c r="A49" s="37" t="inlineStr">
+      <c r="K48" s="6" t="n"/>
+      <c r="L48" s="6" t="n"/>
+      <c r="M48" s="6" t="n"/>
+    </row>
+    <row r="49" ht="15.75" customFormat="1" customHeight="1" s="7">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>select_one yes_no</t>
         </is>
@@ -2263,32 +2251,32 @@
           <t>lymphoedeme</t>
         </is>
       </c>
-      <c r="C49" s="36" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>Presence of Lymphedema</t>
         </is>
       </c>
-      <c r="D49" s="36" t="n"/>
-      <c r="E49" s="36" t="n"/>
-      <c r="F49" s="36" t="n"/>
-      <c r="G49" s="36" t="n"/>
-      <c r="H49" s="37" t="inlineStr">
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="6" t="n"/>
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">${consent} = 'Yes' </t>
         </is>
       </c>
-      <c r="I49" s="36" t="n"/>
+      <c r="I49" s="6" t="n"/>
       <c r="J49" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K49" s="36" t="n"/>
-      <c r="L49" s="36" t="n"/>
-      <c r="M49" s="36" t="n"/>
-    </row>
-    <row r="50" ht="15.75" customFormat="1" customHeight="1" s="37">
-      <c r="A50" s="37" t="inlineStr">
+      <c r="K49" s="6" t="n"/>
+      <c r="L49" s="6" t="n"/>
+      <c r="M49" s="6" t="n"/>
+    </row>
+    <row r="50" ht="15.75" customFormat="1" customHeight="1" s="7">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>select_one yes_no</t>
         </is>
@@ -2298,106 +2286,106 @@
           <t>hydrocele</t>
         </is>
       </c>
-      <c r="C50" s="36" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>Presence of Hydrocele</t>
         </is>
       </c>
-      <c r="D50" s="36" t="n"/>
-      <c r="E50" s="36" t="n"/>
-      <c r="F50" s="36" t="n"/>
-      <c r="G50" s="36" t="n"/>
-      <c r="H50" s="37" t="inlineStr">
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="6" t="n"/>
+      <c r="G50" s="6" t="n"/>
+      <c r="H50" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">${consent} = 'Yes' </t>
         </is>
       </c>
-      <c r="I50" s="36" t="n"/>
+      <c r="I50" s="6" t="n"/>
       <c r="J50" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K50" s="36" t="n"/>
-      <c r="L50" s="36" t="n"/>
-      <c r="M50" s="36" t="n"/>
-    </row>
-    <row r="51" ht="15.75" customFormat="1" customHeight="1" s="37">
+      <c r="K50" s="6" t="n"/>
+      <c r="L50" s="6" t="n"/>
+      <c r="M50" s="6" t="n"/>
+    </row>
+    <row r="51" ht="15.75" customFormat="1" customHeight="1" s="7">
       <c r="B51" s="4" t="n"/>
-      <c r="C51" s="36" t="n"/>
-      <c r="D51" s="36" t="n"/>
-      <c r="E51" s="36" t="n"/>
-      <c r="F51" s="36" t="n"/>
-      <c r="G51" s="36" t="n"/>
-      <c r="I51" s="36" t="n"/>
-      <c r="J51" s="36" t="n"/>
-      <c r="K51" s="36" t="n"/>
-      <c r="L51" s="36" t="n"/>
-      <c r="M51" s="36" t="n"/>
-    </row>
-    <row r="52" ht="31.5" customFormat="1" customHeight="1" s="37">
-      <c r="A52" s="37" t="inlineStr">
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="6" t="n"/>
+      <c r="G51" s="6" t="n"/>
+      <c r="I51" s="6" t="n"/>
+      <c r="J51" s="6" t="n"/>
+      <c r="K51" s="6" t="n"/>
+      <c r="L51" s="6" t="n"/>
+      <c r="M51" s="6" t="n"/>
+    </row>
+    <row r="52" ht="31" customFormat="1" customHeight="1" s="7">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B52" s="36" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>ending_survey_note</t>
         </is>
       </c>
-      <c r="C52" s="36" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>You just entered a value that will end the survey</t>
         </is>
       </c>
-      <c r="D52" s="36" t="n"/>
-      <c r="H52" s="37" t="inlineStr">
+      <c r="D52" s="6" t="n"/>
+      <c r="H52" s="7" t="inlineStr">
         <is>
           <t>${consent} = 'No'</t>
         </is>
       </c>
-      <c r="J52" s="36" t="n"/>
-    </row>
-    <row r="53" customFormat="1" s="37">
-      <c r="A53" s="37" t="inlineStr">
+      <c r="J52" s="6" t="n"/>
+    </row>
+    <row r="53" customFormat="1" s="7">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B53" s="36" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>comments</t>
         </is>
       </c>
-      <c r="C53" s="36" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>Additional Notes</t>
         </is>
       </c>
-      <c r="D53" s="36" t="n"/>
-    </row>
-    <row r="54" customFormat="1" s="37">
-      <c r="B54" s="36" t="n"/>
-      <c r="C54" s="36" t="n"/>
-      <c r="D54" s="36" t="n"/>
-    </row>
-    <row r="55" customFormat="1" s="37">
-      <c r="A55" s="37" t="inlineStr">
+      <c r="D53" s="6" t="n"/>
+    </row>
+    <row r="54" customFormat="1" s="7">
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="6" t="n"/>
+      <c r="D54" s="6" t="n"/>
+    </row>
+    <row r="55" customFormat="1" s="7">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>end repeat</t>
         </is>
       </c>
-      <c r="B55" s="36" t="n"/>
-      <c r="C55" s="36" t="n"/>
-      <c r="D55" s="36" t="n"/>
-    </row>
-    <row r="56" customFormat="1" s="37">
-      <c r="B56" s="36" t="n"/>
-      <c r="C56" s="36" t="n"/>
-      <c r="D56" s="36" t="n"/>
-    </row>
-    <row r="57" customFormat="1" s="37">
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="6" t="n"/>
+    </row>
+    <row r="56" customFormat="1" s="7">
+      <c r="B56" s="6" t="n"/>
+      <c r="C56" s="6" t="n"/>
+      <c r="D56" s="6" t="n"/>
+    </row>
+    <row r="57" customFormat="1" s="7">
       <c r="A57" s="10" t="inlineStr">
         <is>
           <t>calculate</t>
@@ -2430,36 +2418,27 @@
       <c r="N57" s="10" t="n"/>
       <c r="O57" s="10" t="n"/>
     </row>
-    <row r="58" customFormat="1" s="37">
-      <c r="A58" s="37" t="n"/>
-      <c r="B58" s="36" t="n"/>
-      <c r="C58" s="36" t="n"/>
-      <c r="D58" s="36" t="n"/>
-      <c r="E58" s="37" t="n"/>
-      <c r="F58" s="37" t="n"/>
-      <c r="G58" s="37" t="n"/>
-      <c r="H58" s="37" t="n"/>
-      <c r="I58" s="37" t="n"/>
-      <c r="J58" s="37" t="n"/>
-      <c r="K58" s="37" t="n"/>
-      <c r="L58" s="37" t="n"/>
-    </row>
-    <row r="59" customFormat="1" s="37">
-      <c r="A59" s="37" t="inlineStr">
+    <row r="58" customFormat="1" s="7">
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="6" t="n"/>
+    </row>
+    <row r="59" customFormat="1" s="7">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B59" s="36" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="C59" s="36" t="n"/>
-      <c r="D59" s="36" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="6" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="37" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>end</t>
         </is>
@@ -2483,10 +2462,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D26"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.5"/>
   <cols>
-    <col width="14.625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="39.625" customWidth="1" min="2" max="2"/>
+    <col width="14.58203125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="39.58203125" customWidth="1" min="2" max="2"/>
     <col width="23.75" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -2853,11 +2832,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.5"/>
   <cols>
-    <col width="53.375" customWidth="1" min="1" max="1"/>
-    <col width="33.375" customWidth="1" min="2" max="2"/>
-    <col width="15.875" customWidth="1" min="3" max="3"/>
+    <col width="53.33203125" customWidth="1" min="1" max="1"/>
+    <col width="33.33203125" customWidth="1" min="2" max="2"/>
+    <col width="15.83203125" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2878,9 +2857,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="37" t="inlineStr">
-        <is>
-          <t>(Demo) 2. ITAS LF-ONCHO LF Participant From</t>
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>(uganda) 2. ITAS LF-ONCHO LF Participant From</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
